--- a/Result/profitability/6168.xlsx
+++ b/Result/profitability/6168.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07999999999999996</v>
+        <v>0.09374999999999996</v>
       </c>
       <c r="N2" t="n">
-        <v>25.81125</v>
+        <v>25.40875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.16</v>
       </c>
       <c r="N3" t="n">
-        <v>24.85625</v>
+        <v>24.915</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2212499999999999</v>
+        <v>0.23875</v>
       </c>
       <c r="N4" t="n">
-        <v>24.195</v>
+        <v>23.7275</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.20125</v>
+        <v>0.23375</v>
       </c>
       <c r="N5" t="n">
-        <v>22.1475</v>
+        <v>22.09</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21125</v>
+        <v>0.2125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.925</v>
+        <v>19.56</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.20375</v>
+        <v>0.2212499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>18.94</v>
+        <v>19.46375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2725</v>
+        <v>0.28875</v>
       </c>
       <c r="N8" t="n">
-        <v>19.81</v>
+        <v>19.90375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.63</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.305</v>
       </c>
       <c r="N11" t="n">
         <v>19.89625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6168</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>582</v>
+      </c>
+      <c r="D75" t="n">
+        <v>439</v>
+      </c>
+      <c r="E75" t="n">
+        <v>142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02749999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.08625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03161888701517701</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.363636363636363</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4600000000000009</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01845166466105097</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
